--- a/English/GRE/GRE单词.xlsx
+++ b/English/GRE/GRE单词.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Blog\English\GRE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9489A66-C1BE-4908-A08D-390FAB5179B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF6B679A-CF1B-4541-8EA8-B501A3D05D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14865" yWindow="0" windowWidth="13935" windowHeight="16200" activeTab="1" xr2:uid="{44054248-0865-4863-BD19-7134C23342D4}"/>
+    <workbookView xWindow="17685" yWindow="0" windowWidth="11115" windowHeight="16200" activeTab="1" xr2:uid="{44054248-0865-4863-BD19-7134C23342D4}"/>
   </bookViews>
   <sheets>
     <sheet name="地基词" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="1625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2271" uniqueCount="2041">
   <si>
     <t>furtive</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -6436,6 +6436,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>prosaic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>prose</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6512,6 +6516,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>alacrity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>alacrity敏捷</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6529,6 +6537,1662 @@
   </si>
   <si>
     <t>baffling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>puzzle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>confuse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>confound</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>banal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>banal陈腐的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>banality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beguile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intriguing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beguile欺骗，使着迷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>guile诡计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buoy振奋，浮标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buoyant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flamboyant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conciliate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conciliatory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conciliation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uncompromising</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intransigent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>credible可信的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incredible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detrimental有害的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detriment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nocuous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disheartening</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dishearten</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>frustrate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>discourage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fervor热情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zeal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fever发烧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inaccessible难懂的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>indolent懒惰的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>indolence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insolent傲慢的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>invidious烦人的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insidious阴险的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insouciant漫不经心的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insouciance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cavalier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>carefree</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cavalier漫不经心的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chivalrous彬彬有礼的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>knotty复杂的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>knot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thorny</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lethargic昏睡的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lethargy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lethal致命的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inactive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sleepy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pedestrian行人，乏味的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pedal踏板</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quixotic唐吉可德的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>idealistic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>practical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pragmatic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skullduggery欺骗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>utopian乌托邦的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stoicism斯多葛学派，禁欲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>submist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>submissive顺从的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>succumb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suppress抑制、镇压</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oppress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>depress沮丧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vapid乏味的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>absorbing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inviting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>engaging</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beguiling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>acute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>afflict困扰，折磨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>afflictive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>affliction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conflict</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alienate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alien</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alienation异化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>estrange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>animadvert谴责</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>apropos</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>apt适合的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>felicitous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>braggart吹牛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bureaucratic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bureau</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>democracy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bureaucracy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>complement补充</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>compliment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>complete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>complacent自满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>confrontation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>combat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commensurate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>culmination高潮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>climax</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>height</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peak</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>summit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deplore谴责</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deploy部署</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deplorable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>implore恳求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>decry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>divination占卜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>divine神圣的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elucidate阐释</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lucifer路西法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unencumbered</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>encumbrance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>encumber拖累</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impede</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enterprising</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ambitious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>excavate挖掘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>excavation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>evacuate疏散</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exposition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exhibition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>expose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grinding难以忍受的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hinder阻碍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interference干预干涉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interfere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inference</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>limpid清澈的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transparent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>naysay拒绝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gainsay否认</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>naysayer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pellucid透明的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>limpid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>perplex使为难</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>baffle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>perplexing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>polemical好争辩的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dispute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contentious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disputatious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>potency影响力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>potent有力的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impotent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preoccupied专注的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>occupy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>occupation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>concentrate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pushover容易做</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>replete充满的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deplete耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rudimentary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rudiment雏形</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elementary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fundamental</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trade-off</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tranquil平静的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tranquilize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abound</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>replete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coalesce合并</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coalescent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coalition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>decadence堕落</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>decadent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>corruption</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>degenerate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>degeneracy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>discount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>discrete离散的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>discretion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>discreet谨慎的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>garrulous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>garrulous话多的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loquacious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>importunate纠缠不休</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>importune</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pester强求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intoxicate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intoxicate醉酒，入迷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mercurial多变的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>capricious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mercury</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fickle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neutralize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overt明显的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overtly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>covert隐蔽的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>perfunctory敷衍的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>proliferate繁殖，激增</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>surge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>balloon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>repertoire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>repository仓库</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>serene宁静的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>serenity宁静</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scene场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tranquil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stagnate停滞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stagnant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stigma污点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>undermine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>undergird加固</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aberrant异常的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aberrance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>authoritative权威的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>authoritarian独裁的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blithe漫不经心的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insouciant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blur</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blurred</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalyse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalyst催化剂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>charisma</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>charismatic有魅力的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conundrum谜题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>countercat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cagey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cunning狡猾的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detract贬低</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>distract分心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diminish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disposition性情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disposal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dispose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>duplicitous奸诈的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dupe欺骗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disingenuous不老实的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>egalitarian平等主义</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>evangelical福音的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>entertaining</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>entertainment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>feckless软弱的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>futile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>histrionic装腔作势的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>historical历史的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>historic有历史意义的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plastic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mannered</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imperturbable冷静的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disturb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incontrovertible不容置疑的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>controversy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>indisputable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>undoubted</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mainstay支柱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>megalomania</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>megalomaniacal自大狂的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mania</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>magnificent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>magnanimous大度的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>munificent慷慨的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nebulous模糊的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nettlesome棘手的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>irksome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vexing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>palpable可感知的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impalpable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>paragon典范</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>paradigm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prototype</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pertinent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stump树桩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>taciturn沉默寡言的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tangible可感知的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intangible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>compromise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unyielding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>volatile不稳定的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>volatility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>violent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mercurial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>affinity亲密</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>affiliated</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>analogy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>analogous类比的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boisterous喧闹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clamorous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>celebrity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>celebrate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commence开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commencement毕业典礼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dim</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>faint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dampen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>extravagant奢侈的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>extrapolate推测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exaggerate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flatter奉承，谄媚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>idiosyncrasy个人特质</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>idiosyncratic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imperative命令的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>magisterial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>infinite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>finite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>infinity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lingering拖延的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>linger逗留</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>minuscule极少的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>panacea灵丹妙药</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elixir灵丹妙药</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>revisionist修正主义</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>revise修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slack松的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slack off</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spur</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>activate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>check限制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>univocal单一意思</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>equivocal模棱两可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pretentious张扬的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unpretentious谦逊的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>presumptuous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assuage平息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assuagement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>persuade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ease</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mitigate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alleviate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>relieve</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>baroque</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contemplate沉思</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>debilitate使虚弱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>debilitation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>feckless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>debunk揭穿真相</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>distaste厌恶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>apprehensive担忧的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>distasteful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dislike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hostile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hostility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hospitality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intricate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intrigue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intricacy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>melody</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>malady顽疾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>malign</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>misconception</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preconception偏见</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obeisance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obedient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ornament装饰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>decoration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ornamental</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overload</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plague</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pandemic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>afflict</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>epidemic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plentitude</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preclude排除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exclude</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>privation贫困</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>private</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>profuse丰富的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>profusion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>extravagant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lavish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resonate共鸣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resurgence复兴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resurrection复兴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sectarian教派的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sector</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nepotism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>secretary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>solitude独居</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>solidarity结实</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>solicitude关怀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>solicit请求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>solicitous关心的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sycophantic谄媚的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sycophant谄媚者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wary提防的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flattering</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unwary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wont</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abhor憎恨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abhorrent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loathe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abominate憎恨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abominable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abomination</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anecdote</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anecdotal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anonymous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anonym</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nominate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspirant有抱负的人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspiration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspirational</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>respire呼吸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>confessional忏悔的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>profess说</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>content内容，目录，满意</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contend争论</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dilemma</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>difficulty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disciplined</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>self-disciplined</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disdain蔑视</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disdainful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>egregious惊人的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gregarious群居的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sociable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enchant使着迷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enchanting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disenchant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>encomium颂词，赞美</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10880,52 +12544,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="A1" s="9">
+      <c r="A1" s="11">
         <v>1</v>
       </c>
-      <c r="B1" s="9">
+      <c r="B1" s="11">
         <v>2</v>
       </c>
-      <c r="C1" s="9">
+      <c r="C1" s="11">
         <v>3</v>
       </c>
-      <c r="D1" s="9">
+      <c r="D1" s="11">
         <v>4</v>
       </c>
-      <c r="E1" s="9">
+      <c r="E1" s="11">
         <v>5</v>
       </c>
-      <c r="F1" s="9">
+      <c r="F1" s="11">
         <v>6</v>
       </c>
-      <c r="G1" s="9">
+      <c r="G1" s="11">
         <v>7</v>
       </c>
-      <c r="H1" s="9">
+      <c r="H1" s="11">
         <v>8</v>
       </c>
-      <c r="I1" s="9">
+      <c r="I1" s="11">
         <v>9</v>
       </c>
       <c r="J1" s="11">
         <v>10</v>
       </c>
-      <c r="K1" s="9">
+      <c r="K1" s="11">
         <v>11</v>
       </c>
-      <c r="L1" s="9">
+      <c r="L1" s="11">
         <v>12</v>
       </c>
-      <c r="M1" s="9">
+      <c r="M1" s="11">
         <v>13</v>
       </c>
-      <c r="N1" s="9">
+      <c r="N1" s="11">
         <v>14</v>
       </c>
-      <c r="O1" s="9">
+      <c r="O1" s="11">
         <v>15</v>
       </c>
-      <c r="P1" s="9">
+      <c r="P1" s="11">
         <v>16</v>
       </c>
       <c r="Q1" s="9">
@@ -11060,14 +12724,26 @@
         <v>1524</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>1620</v>
-      </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
+        <v>1622</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>1694</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>1787</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>1832</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>1901</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>1942</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>2008</v>
+      </c>
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
@@ -11132,14 +12808,26 @@
         <v>1525</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>1621</v>
-      </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
+        <v>1623</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>1695</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>1788</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>1833</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>1902</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>1640</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>2009</v>
+      </c>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
@@ -11206,12 +12894,24 @@
       <c r="J4" s="3" t="s">
         <v>1450</v>
       </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
+      <c r="K4" s="3" t="s">
+        <v>1634</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>1789</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>1312</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>1904</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>1943</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>2010</v>
+      </c>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
@@ -11278,12 +12978,24 @@
       <c r="J5" s="3" t="s">
         <v>1559</v>
       </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
+      <c r="K5" s="3" t="s">
+        <v>1696</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>1790</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>1311</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>1903</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>1944</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>2011</v>
+      </c>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
@@ -11348,14 +13060,26 @@
         <v>1435</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>1622</v>
-      </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
+        <v>1624</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>1791</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>1835</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>1905</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>1945</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>2012</v>
+      </c>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
@@ -11422,12 +13146,24 @@
       <c r="J7" s="3" t="s">
         <v>1449</v>
       </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
+      <c r="K7" s="3" t="s">
+        <v>1698</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>1792</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>1499</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>1906</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>1946</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>2013</v>
+      </c>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
@@ -11494,12 +13230,24 @@
       <c r="J8" s="3" t="s">
         <v>1452</v>
       </c>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
+      <c r="K8" s="3" t="s">
+        <v>1621</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>1793</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>1834</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>1907</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>1947</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>2014</v>
+      </c>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
@@ -11564,14 +13312,26 @@
         <v>1530</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>1623</v>
-      </c>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
+        <v>1625</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>1699</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>1794</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>1836</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>1908</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>1948</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>2015</v>
+      </c>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
@@ -11636,14 +13396,26 @@
         <v>1529</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>1624</v>
-      </c>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
+        <v>1626</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>1795</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>1665</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>1909</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>1949</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>2016</v>
+      </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
@@ -11707,13 +13479,27 @@
       <c r="I11" s="3" t="s">
         <v>1512</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
+      <c r="J11" s="3" t="s">
+        <v>1627</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>1701</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>1796</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>1837</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>1910</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>1950</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>2017</v>
+      </c>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
@@ -11777,13 +13563,27 @@
       <c r="I12" s="3" t="s">
         <v>1531</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
+      <c r="J12" s="3" t="s">
+        <v>1628</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>1702</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>1797</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>1838</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>1911</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>1951</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>2018</v>
+      </c>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
@@ -11847,13 +13647,27 @@
       <c r="I13" s="3" t="s">
         <v>1532</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
+      <c r="J13" s="3" t="s">
+        <v>1629</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>1703</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>1242</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>1839</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>1912</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>1952</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>2019</v>
+      </c>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
@@ -11917,13 +13731,27 @@
       <c r="I14" s="3" t="s">
         <v>1533</v>
       </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
+      <c r="J14" s="3" t="s">
+        <v>1631</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>1704</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>1243</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>1841</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>1913</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>1953</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>2020</v>
+      </c>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
@@ -11987,13 +13815,27 @@
       <c r="I15" s="3" t="s">
         <v>1534</v>
       </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
+      <c r="J15" s="3" t="s">
+        <v>1632</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>1705</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>1798</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>1840</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>1914</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>1954</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>2021</v>
+      </c>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
@@ -12057,13 +13899,27 @@
       <c r="I16" s="3" t="s">
         <v>1535</v>
       </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
+      <c r="J16" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>1706</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>1421</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>1843</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>1915</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>2022</v>
+      </c>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
@@ -12127,13 +13983,27 @@
       <c r="I17" s="3" t="s">
         <v>1465</v>
       </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
+      <c r="J17" s="3" t="s">
+        <v>1635</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>1707</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>1799</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>1842</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>1916</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>1955</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>2023</v>
+      </c>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
@@ -12197,13 +14067,27 @@
       <c r="I18" s="3" t="s">
         <v>1536</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
+      <c r="J18" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>1709</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>1800</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>1844</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>1917</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>1957</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>1742</v>
+      </c>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
@@ -12267,13 +14151,27 @@
       <c r="I19" s="3" t="s">
         <v>1537</v>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
+      <c r="J19" s="3" t="s">
+        <v>1634</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>1708</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>1802</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>1248</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>1918</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>1958</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>1743</v>
+      </c>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
@@ -12337,13 +14235,27 @@
       <c r="I20" s="3" t="s">
         <v>1538</v>
       </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
+      <c r="J20" s="3" t="s">
+        <v>1636</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>1525</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>1572</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>1845</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>1919</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>1959</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>2024</v>
+      </c>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
@@ -12407,13 +14319,27 @@
       <c r="I21" s="3" t="s">
         <v>1541</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
+      <c r="J21" s="3" t="s">
+        <v>1637</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>1710</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>1571</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>1813</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>1920</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>1960</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>2025</v>
+      </c>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
@@ -12462,8 +14388,8 @@
       <c r="D22" s="3" t="s">
         <v>1107</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>1208</v>
+      <c r="E22" s="10" t="s">
+        <v>1956</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>1319</v>
@@ -12477,13 +14403,27 @@
       <c r="I22" s="3" t="s">
         <v>1540</v>
       </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
+      <c r="J22" s="3" t="s">
+        <v>1638</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>1711</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>1803</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>1847</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>1921</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>1961</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>2026</v>
+      </c>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
@@ -12533,7 +14473,7 @@
         <v>1108</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>1320</v>
@@ -12547,13 +14487,27 @@
       <c r="I23" s="3" t="s">
         <v>1542</v>
       </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
+      <c r="J23" s="3" t="s">
+        <v>1639</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>1712</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>1804</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>1846</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>1922</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>1962</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>2027</v>
+      </c>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
@@ -12603,7 +14557,7 @@
         <v>1109</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>1321</v>
@@ -12617,13 +14571,27 @@
       <c r="I24" s="3" t="s">
         <v>1543</v>
       </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
+      <c r="J24" s="3" t="s">
+        <v>1640</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>1694</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>1805</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>1848</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>1923</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>1963</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>2028</v>
+      </c>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
@@ -12673,7 +14641,7 @@
         <v>1110</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>1322</v>
@@ -12687,13 +14655,27 @@
       <c r="I25" s="3" t="s">
         <v>1544</v>
       </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
+      <c r="J25" s="3" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>1713</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>1806</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>1830</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>1924</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>1359</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>2029</v>
+      </c>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
@@ -12743,7 +14725,7 @@
         <v>244</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>1323</v>
@@ -12757,13 +14739,27 @@
       <c r="I26" s="3" t="s">
         <v>1545</v>
       </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
+      <c r="J26" s="3" t="s">
+        <v>1642</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>1714</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>1379</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>1849</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>1901</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>1964</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>2030</v>
+      </c>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
@@ -12813,7 +14809,7 @@
         <v>1111</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>1324</v>
@@ -12827,13 +14823,27 @@
       <c r="I27" s="3" t="s">
         <v>1546</v>
       </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
+      <c r="J27" s="3" t="s">
+        <v>1643</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>1715</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>1377</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>1850</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>1558</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>2031</v>
+      </c>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
@@ -12883,7 +14893,7 @@
         <v>1112</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>1325</v>
@@ -12897,13 +14907,27 @@
       <c r="I28" s="3" t="s">
         <v>1547</v>
       </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
+      <c r="J28" s="3" t="s">
+        <v>1644</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>1716</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>1808</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>1342</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>1925</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>1966</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>2032</v>
+      </c>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
@@ -12953,7 +14977,7 @@
         <v>1113</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>1326</v>
@@ -12967,13 +14991,27 @@
       <c r="I29" s="3" t="s">
         <v>1548</v>
       </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-      <c r="O29" s="3"/>
-      <c r="P29" s="3"/>
+      <c r="J29" s="3" t="s">
+        <v>1645</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>1717</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>1851</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>1926</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>1965</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>1324</v>
+      </c>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
@@ -13023,7 +15061,7 @@
         <v>1114</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>1327</v>
@@ -13037,13 +15075,27 @@
       <c r="I30" s="3" t="s">
         <v>1549</v>
       </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-      <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
+      <c r="J30" s="3" t="s">
+        <v>1646</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>1718</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>1633</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>1852</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>1927</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>1967</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>2033</v>
+      </c>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
@@ -13093,7 +15145,7 @@
         <v>1115</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>1328</v>
@@ -13107,13 +15159,27 @@
       <c r="I31" s="3" t="s">
         <v>1550</v>
       </c>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
-      <c r="P31" s="3"/>
+      <c r="J31" s="3" t="s">
+        <v>1647</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>1719</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>1809</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>1853</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>1850</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>1968</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>2034</v>
+      </c>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
@@ -13163,7 +15229,7 @@
         <v>1117</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>1329</v>
@@ -13177,13 +15243,27 @@
       <c r="I32" s="3" t="s">
         <v>1551</v>
       </c>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
+      <c r="J32" s="3" t="s">
+        <v>1227</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>1720</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>1810</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>1854</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>1928</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>1969</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>1350</v>
+      </c>
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
@@ -13233,7 +15313,7 @@
         <v>1116</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>1320</v>
@@ -13247,13 +15327,27 @@
       <c r="I33" s="3" t="s">
         <v>1552</v>
       </c>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
-      <c r="P33" s="3"/>
+      <c r="J33" s="3" t="s">
+        <v>1648</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>1721</v>
+      </c>
+      <c r="L33" s="10" t="s">
+        <v>1812</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>1855</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>1929</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>1970</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>1646</v>
+      </c>
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
@@ -13303,7 +15397,7 @@
         <v>1118</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>1330</v>
@@ -13317,13 +15411,27 @@
       <c r="I34" s="3" t="s">
         <v>1553</v>
       </c>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
-      <c r="O34" s="3"/>
-      <c r="P34" s="3"/>
+      <c r="J34" s="3" t="s">
+        <v>1649</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>1702</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>1811</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>1930</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>1971</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>2035</v>
+      </c>
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
@@ -13373,7 +15481,7 @@
         <v>1119</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>1317</v>
@@ -13387,13 +15495,27 @@
       <c r="I35" s="3" t="s">
         <v>1554</v>
       </c>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3"/>
-      <c r="O35" s="3"/>
-      <c r="P35" s="3"/>
+      <c r="J35" s="3" t="s">
+        <v>1650</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>1722</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>1448</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>1857</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>1931</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>1972</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>2036</v>
+      </c>
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
@@ -13443,7 +15565,7 @@
         <v>1120</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>1331</v>
@@ -13457,13 +15579,27 @@
       <c r="I36" s="3" t="s">
         <v>1555</v>
       </c>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3"/>
-      <c r="O36" s="3"/>
-      <c r="P36" s="3"/>
+      <c r="J36" s="3" t="s">
+        <v>1651</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>1447</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>1858</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>1932</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>1973</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>2037</v>
+      </c>
       <c r="Q36" s="3"/>
       <c r="R36" s="3"/>
       <c r="S36" s="3"/>
@@ -13513,7 +15649,7 @@
         <v>1121</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>1332</v>
@@ -13527,13 +15663,27 @@
       <c r="I37" s="3" t="s">
         <v>1556</v>
       </c>
-      <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3"/>
-      <c r="O37" s="3"/>
-      <c r="P37" s="3"/>
+      <c r="J37" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>1723</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>1813</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>1859</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>1933</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>1974</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>2038</v>
+      </c>
       <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
       <c r="S37" s="3"/>
@@ -13583,7 +15733,7 @@
         <v>1122</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>1333</v>
@@ -13597,13 +15747,27 @@
       <c r="I38" s="10" t="s">
         <v>1557</v>
       </c>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="3"/>
-      <c r="O38" s="3"/>
-      <c r="P38" s="3"/>
+      <c r="J38" s="3" t="s">
+        <v>1653</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>1724</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>1814</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>1860</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>1934</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>1975</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>2039</v>
+      </c>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
@@ -13653,7 +15817,7 @@
         <v>1123</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>1334</v>
@@ -13667,13 +15831,27 @@
       <c r="I39" s="3" t="s">
         <v>1558</v>
       </c>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
-      <c r="O39" s="3"/>
-      <c r="P39" s="3"/>
+      <c r="J39" s="3" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>1725</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>1815</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>1861</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>1935</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>1976</v>
+      </c>
+      <c r="P39" s="3" t="s">
+        <v>1633</v>
+      </c>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
@@ -13723,7 +15901,7 @@
         <v>1124</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>1335</v>
@@ -13737,13 +15915,27 @@
       <c r="I40" s="3" t="s">
         <v>1559</v>
       </c>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
-      <c r="O40" s="3"/>
-      <c r="P40" s="3"/>
+      <c r="J40" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>1726</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>1816</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>1771</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>1936</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>1977</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>1807</v>
+      </c>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
@@ -13793,7 +15985,7 @@
         <v>1125</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>1336</v>
@@ -13807,13 +15999,27 @@
       <c r="I41" s="3" t="s">
         <v>1450</v>
       </c>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="3"/>
+      <c r="J41" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>1727</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>1817</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>1862</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>1937</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>1978</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>2040</v>
+      </c>
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3"/>
@@ -13863,7 +16069,7 @@
         <v>1126</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>1337</v>
@@ -13877,12 +16083,24 @@
       <c r="I42" s="3" t="s">
         <v>1449</v>
       </c>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
-      <c r="O42" s="3"/>
+      <c r="J42" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>1728</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>1818</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>1863</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>1938</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>1979</v>
+      </c>
       <c r="P42" s="3"/>
       <c r="Q42" s="3"/>
       <c r="R42" s="3"/>
@@ -13933,7 +16151,7 @@
         <v>1127</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>1338</v>
@@ -13947,12 +16165,24 @@
       <c r="I43" s="3" t="s">
         <v>1452</v>
       </c>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
-      <c r="M43" s="3"/>
-      <c r="N43" s="3"/>
-      <c r="O43" s="3"/>
+      <c r="J43" s="3" t="s">
+        <v>1559</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>1729</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>1460</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>1865</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>1940</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>1980</v>
+      </c>
       <c r="P43" s="3"/>
       <c r="Q43" s="3"/>
       <c r="R43" s="3"/>
@@ -14003,7 +16233,7 @@
         <v>247</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>1339</v>
@@ -14017,12 +16247,24 @@
       <c r="I44" s="3" t="s">
         <v>1560</v>
       </c>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3"/>
-      <c r="N44" s="3"/>
-      <c r="O44" s="3"/>
+      <c r="J44" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>1730</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>1819</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>1864</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>1939</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>1981</v>
+      </c>
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
       <c r="R44" s="3"/>
@@ -14073,7 +16315,7 @@
         <v>1128</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>1340</v>
@@ -14087,12 +16329,24 @@
       <c r="I45" s="3" t="s">
         <v>1561</v>
       </c>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="3"/>
-      <c r="M45" s="3"/>
-      <c r="N45" s="3"/>
-      <c r="O45" s="3"/>
+      <c r="J45" s="3" t="s">
+        <v>1660</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>1731</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>1820</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>1866</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>1941</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>1982</v>
+      </c>
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
@@ -14143,7 +16397,7 @@
         <v>248</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>1341</v>
@@ -14157,12 +16411,24 @@
       <c r="I46" s="3" t="s">
         <v>1562</v>
       </c>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3"/>
-      <c r="M46" s="3"/>
-      <c r="N46" s="3"/>
-      <c r="O46" s="3"/>
+      <c r="J46" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>1732</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>1822</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>1867</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>1639</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>1564</v>
+      </c>
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
       <c r="R46" s="3"/>
@@ -14213,7 +16479,7 @@
         <v>1129</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>1342</v>
@@ -14227,12 +16493,22 @@
       <c r="I47" s="3" t="s">
         <v>1563</v>
       </c>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
+      <c r="J47" s="3" t="s">
+        <v>1662</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>1323</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>1821</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>1533</v>
+      </c>
       <c r="N47" s="3"/>
-      <c r="O47" s="3"/>
+      <c r="O47" s="3" t="s">
+        <v>1983</v>
+      </c>
       <c r="P47" s="3"/>
       <c r="Q47" s="3"/>
       <c r="R47" s="3"/>
@@ -14283,7 +16559,7 @@
         <v>1130</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>1343</v>
@@ -14297,12 +16573,22 @@
       <c r="I48" s="3" t="s">
         <v>1564</v>
       </c>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3"/>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3"/>
+      <c r="J48" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>1823</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>1868</v>
+      </c>
       <c r="N48" s="3"/>
-      <c r="O48" s="3"/>
+      <c r="O48" s="3" t="s">
+        <v>1984</v>
+      </c>
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
       <c r="R48" s="3"/>
@@ -14353,7 +16639,7 @@
         <v>249</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>1344</v>
@@ -14367,12 +16653,22 @@
       <c r="I49" s="3" t="s">
         <v>1565</v>
       </c>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
+      <c r="J49" s="10" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>1325</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>1824</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>1869</v>
+      </c>
       <c r="N49" s="3"/>
-      <c r="O49" s="3"/>
+      <c r="O49" s="3" t="s">
+        <v>1985</v>
+      </c>
       <c r="P49" s="3"/>
       <c r="Q49" s="3"/>
       <c r="R49" s="3"/>
@@ -14423,7 +16719,7 @@
         <v>1136</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>1345</v>
@@ -14437,12 +16733,22 @@
       <c r="I50" s="3" t="s">
         <v>1566</v>
       </c>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="3"/>
-      <c r="M50" s="3"/>
+      <c r="J50" s="3" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>1707</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>1825</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>1870</v>
+      </c>
       <c r="N50" s="3"/>
-      <c r="O50" s="3"/>
+      <c r="O50" s="3" t="s">
+        <v>1986</v>
+      </c>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
       <c r="R50" s="3"/>
@@ -14493,7 +16799,7 @@
         <v>1131</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>1346</v>
@@ -14507,12 +16813,22 @@
       <c r="I51" s="3" t="s">
         <v>1567</v>
       </c>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="3"/>
-      <c r="M51" s="3"/>
+      <c r="J51" s="3" t="s">
+        <v>1667</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>1734</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>1826</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>1871</v>
+      </c>
       <c r="N51" s="3"/>
-      <c r="O51" s="3"/>
+      <c r="O51" s="3" t="s">
+        <v>1787</v>
+      </c>
       <c r="P51" s="3"/>
       <c r="Q51" s="3"/>
       <c r="R51" s="3"/>
@@ -14563,7 +16879,7 @@
         <v>206</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>1347</v>
@@ -14577,12 +16893,22 @@
       <c r="I52" s="3" t="s">
         <v>1568</v>
       </c>
-      <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
+      <c r="J52" s="3" t="s">
+        <v>1668</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>1735</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>1827</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>1872</v>
+      </c>
       <c r="N52" s="3"/>
-      <c r="O52" s="3"/>
+      <c r="O52" s="3" t="s">
+        <v>1788</v>
+      </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
@@ -14633,7 +16959,7 @@
         <v>210</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>1348</v>
@@ -14647,12 +16973,22 @@
       <c r="I53" s="3" t="s">
         <v>1569</v>
       </c>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
-      <c r="L53" s="3"/>
-      <c r="M53" s="3"/>
+      <c r="J53" s="3" t="s">
+        <v>1666</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>1736</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>1828</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>1873</v>
+      </c>
       <c r="N53" s="3"/>
-      <c r="O53" s="3"/>
+      <c r="O53" s="3" t="s">
+        <v>1987</v>
+      </c>
       <c r="P53" s="3"/>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -14703,7 +17039,7 @@
         <v>1135</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>1349</v>
@@ -14715,12 +17051,22 @@
       <c r="I54" s="3" t="s">
         <v>1570</v>
       </c>
-      <c r="J54" s="3"/>
-      <c r="K54" s="3"/>
-      <c r="L54" s="3"/>
-      <c r="M54" s="3"/>
+      <c r="J54" s="3" t="s">
+        <v>1669</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>1737</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>1658</v>
+      </c>
       <c r="N54" s="3"/>
-      <c r="O54" s="3"/>
+      <c r="O54" s="3" t="s">
+        <v>1988</v>
+      </c>
       <c r="P54" s="3"/>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
@@ -14771,7 +17117,7 @@
         <v>1132</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>1350</v>
@@ -14783,12 +17129,22 @@
       <c r="I55" s="3" t="s">
         <v>1571</v>
       </c>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
+      <c r="J55" s="3" t="s">
+        <v>1670</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>1740</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>1830</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>1660</v>
+      </c>
       <c r="N55" s="3"/>
-      <c r="O55" s="3"/>
+      <c r="O55" s="3" t="s">
+        <v>1989</v>
+      </c>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
@@ -14839,7 +17195,7 @@
         <v>1133</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>1351</v>
@@ -14851,12 +17207,22 @@
       <c r="I56" s="3" t="s">
         <v>1572</v>
       </c>
-      <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
-      <c r="L56" s="3"/>
-      <c r="M56" s="3"/>
+      <c r="J56" s="3" t="s">
+        <v>1671</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>1738</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>1831</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>1874</v>
+      </c>
       <c r="N56" s="3"/>
-      <c r="O56" s="3"/>
+      <c r="O56" s="3" t="s">
+        <v>1990</v>
+      </c>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
@@ -14907,7 +17273,7 @@
         <v>1134</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>1352</v>
@@ -14919,12 +17285,20 @@
       <c r="I57" s="3" t="s">
         <v>1275</v>
       </c>
-      <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
+      <c r="J57" s="3" t="s">
+        <v>1672</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>1739</v>
+      </c>
       <c r="L57" s="3"/>
-      <c r="M57" s="3"/>
+      <c r="M57" s="3" t="s">
+        <v>1876</v>
+      </c>
       <c r="N57" s="3"/>
-      <c r="O57" s="3"/>
+      <c r="O57" s="3" t="s">
+        <v>1991</v>
+      </c>
       <c r="P57" s="3"/>
       <c r="Q57" s="3"/>
       <c r="R57" s="3"/>
@@ -14975,7 +17349,7 @@
         <v>1138</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>1353</v>
@@ -14987,12 +17361,20 @@
       <c r="I58" s="3" t="s">
         <v>1573</v>
       </c>
-      <c r="J58" s="3"/>
-      <c r="K58" s="3"/>
+      <c r="J58" s="3" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>1741</v>
+      </c>
       <c r="L58" s="3"/>
-      <c r="M58" s="3"/>
+      <c r="M58" s="3" t="s">
+        <v>1875</v>
+      </c>
       <c r="N58" s="3"/>
-      <c r="O58" s="3"/>
+      <c r="O58" s="3" t="s">
+        <v>1992</v>
+      </c>
       <c r="P58" s="3"/>
       <c r="Q58" s="3"/>
       <c r="R58" s="3"/>
@@ -15043,7 +17425,7 @@
         <v>1137</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>1354</v>
@@ -15055,12 +17437,20 @@
       <c r="I59" s="3" t="s">
         <v>1560</v>
       </c>
-      <c r="J59" s="3"/>
-      <c r="K59" s="3"/>
+      <c r="J59" s="3" t="s">
+        <v>1674</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>1742</v>
+      </c>
       <c r="L59" s="3"/>
-      <c r="M59" s="3"/>
+      <c r="M59" s="3" t="s">
+        <v>1877</v>
+      </c>
       <c r="N59" s="3"/>
-      <c r="O59" s="3"/>
+      <c r="O59" s="3" t="s">
+        <v>1993</v>
+      </c>
       <c r="P59" s="3"/>
       <c r="Q59" s="3"/>
       <c r="R59" s="3"/>
@@ -15111,7 +17501,7 @@
         <v>283</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>1355</v>
@@ -15123,12 +17513,20 @@
       <c r="I60" s="3" t="s">
         <v>1574</v>
       </c>
-      <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
+      <c r="J60" s="3" t="s">
+        <v>1675</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>1743</v>
+      </c>
       <c r="L60" s="3"/>
-      <c r="M60" s="3"/>
+      <c r="M60" s="3" t="s">
+        <v>1878</v>
+      </c>
       <c r="N60" s="3"/>
-      <c r="O60" s="3"/>
+      <c r="O60" s="3" t="s">
+        <v>1484</v>
+      </c>
       <c r="P60" s="3"/>
       <c r="Q60" s="3"/>
       <c r="R60" s="3"/>
@@ -15179,7 +17577,7 @@
         <v>254</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>1356</v>
@@ -15191,12 +17589,20 @@
       <c r="I61" s="3" t="s">
         <v>1575</v>
       </c>
-      <c r="J61" s="3"/>
-      <c r="K61" s="3"/>
+      <c r="J61" s="3" t="s">
+        <v>1676</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>1744</v>
+      </c>
       <c r="L61" s="3"/>
-      <c r="M61" s="3"/>
+      <c r="M61" s="3" t="s">
+        <v>1499</v>
+      </c>
       <c r="N61" s="3"/>
-      <c r="O61" s="3"/>
+      <c r="O61" s="3" t="s">
+        <v>1994</v>
+      </c>
       <c r="P61" s="3"/>
       <c r="Q61" s="3"/>
       <c r="R61" s="3"/>
@@ -15247,7 +17653,7 @@
         <v>1139</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>1357</v>
@@ -15259,12 +17665,20 @@
       <c r="I62" s="3" t="s">
         <v>1576</v>
       </c>
-      <c r="J62" s="3"/>
-      <c r="K62" s="3"/>
+      <c r="J62" s="3" t="s">
+        <v>1677</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>1745</v>
+      </c>
       <c r="L62" s="3"/>
-      <c r="M62" s="3"/>
+      <c r="M62" s="3" t="s">
+        <v>1879</v>
+      </c>
       <c r="N62" s="3"/>
-      <c r="O62" s="3"/>
+      <c r="O62" s="3" t="s">
+        <v>1995</v>
+      </c>
       <c r="P62" s="3"/>
       <c r="Q62" s="3"/>
       <c r="R62" s="3"/>
@@ -15315,7 +17729,7 @@
         <v>1140</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>1358</v>
@@ -15327,12 +17741,20 @@
       <c r="I63" s="3" t="s">
         <v>1534</v>
       </c>
-      <c r="J63" s="3"/>
-      <c r="K63" s="3"/>
+      <c r="J63" s="3" t="s">
+        <v>1678</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>1746</v>
+      </c>
       <c r="L63" s="3"/>
-      <c r="M63" s="3"/>
+      <c r="M63" s="3" t="s">
+        <v>1875</v>
+      </c>
       <c r="N63" s="3"/>
-      <c r="O63" s="3"/>
+      <c r="O63" s="3" t="s">
+        <v>1996</v>
+      </c>
       <c r="P63" s="3"/>
       <c r="Q63" s="3"/>
       <c r="R63" s="3"/>
@@ -15383,7 +17805,7 @@
         <v>1141</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>1227</v>
@@ -15395,12 +17817,20 @@
       <c r="I64" s="3" t="s">
         <v>1577</v>
       </c>
-      <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
+      <c r="J64" s="3" t="s">
+        <v>1601</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>1747</v>
+      </c>
       <c r="L64" s="3"/>
-      <c r="M64" s="3"/>
+      <c r="M64" s="3" t="s">
+        <v>1880</v>
+      </c>
       <c r="N64" s="3"/>
-      <c r="O64" s="3"/>
+      <c r="O64" s="10" t="s">
+        <v>1997</v>
+      </c>
       <c r="P64" s="3"/>
       <c r="Q64" s="3"/>
       <c r="R64" s="3"/>
@@ -15451,7 +17881,7 @@
         <v>1142</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>1359</v>
@@ -15463,12 +17893,20 @@
       <c r="I65" s="3" t="s">
         <v>1578</v>
       </c>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
+      <c r="J65" s="3" t="s">
+        <v>1630</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>1748</v>
+      </c>
       <c r="L65" s="3"/>
-      <c r="M65" s="3"/>
+      <c r="M65" s="3" t="s">
+        <v>1879</v>
+      </c>
       <c r="N65" s="3"/>
-      <c r="O65" s="3"/>
+      <c r="O65" s="3" t="s">
+        <v>1998</v>
+      </c>
       <c r="P65" s="3"/>
       <c r="Q65" s="3"/>
       <c r="R65" s="3"/>
@@ -15519,7 +17957,7 @@
         <v>255</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>1266</v>
@@ -15531,12 +17969,20 @@
       <c r="I66" s="3" t="s">
         <v>1579</v>
       </c>
-      <c r="J66" s="3"/>
-      <c r="K66" s="3"/>
+      <c r="J66" s="3" t="s">
+        <v>1679</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>1749</v>
+      </c>
       <c r="L66" s="3"/>
-      <c r="M66" s="3"/>
+      <c r="M66" s="3" t="s">
+        <v>1881</v>
+      </c>
       <c r="N66" s="3"/>
-      <c r="O66" s="3"/>
+      <c r="O66" s="3" t="s">
+        <v>1999</v>
+      </c>
       <c r="P66" s="3"/>
       <c r="Q66" s="3"/>
       <c r="R66" s="3"/>
@@ -15587,7 +18033,7 @@
         <v>1143</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>1360</v>
@@ -15599,12 +18045,20 @@
       <c r="I67" s="3" t="s">
         <v>1580</v>
       </c>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
+      <c r="J67" s="10" t="s">
+        <v>1684</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>1750</v>
+      </c>
       <c r="L67" s="3"/>
-      <c r="M67" s="3"/>
+      <c r="M67" s="3" t="s">
+        <v>1839</v>
+      </c>
       <c r="N67" s="3"/>
-      <c r="O67" s="3"/>
+      <c r="O67" s="3" t="s">
+        <v>2000</v>
+      </c>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
@@ -15655,7 +18109,7 @@
         <v>1144</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>1361</v>
@@ -15667,12 +18121,20 @@
       <c r="I68" s="3" t="s">
         <v>1581</v>
       </c>
-      <c r="J68" s="3"/>
-      <c r="K68" s="3"/>
+      <c r="J68" s="3" t="s">
+        <v>1680</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>1751</v>
+      </c>
       <c r="L68" s="3"/>
-      <c r="M68" s="3"/>
+      <c r="M68" s="3" t="s">
+        <v>1450</v>
+      </c>
       <c r="N68" s="3"/>
-      <c r="O68" s="3"/>
+      <c r="O68" s="3" t="s">
+        <v>2001</v>
+      </c>
       <c r="P68" s="3"/>
       <c r="Q68" s="3"/>
       <c r="R68" s="3"/>
@@ -15723,7 +18185,7 @@
         <v>1145</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>1362</v>
@@ -15735,12 +18197,20 @@
       <c r="I69" s="3" t="s">
         <v>1582</v>
       </c>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3"/>
+      <c r="J69" s="3" t="s">
+        <v>1681</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>1741</v>
+      </c>
       <c r="L69" s="3"/>
-      <c r="M69" s="3"/>
+      <c r="M69" s="3" t="s">
+        <v>1449</v>
+      </c>
       <c r="N69" s="3"/>
-      <c r="O69" s="3"/>
+      <c r="O69" s="3" t="s">
+        <v>2002</v>
+      </c>
       <c r="P69" s="3"/>
       <c r="Q69" s="3"/>
       <c r="R69" s="3"/>
@@ -15791,7 +18261,7 @@
         <v>1146</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>1363</v>
@@ -15803,12 +18273,20 @@
       <c r="I70" s="3" t="s">
         <v>1583</v>
       </c>
-      <c r="J70" s="3"/>
-      <c r="K70" s="3"/>
+      <c r="J70" s="3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>1740</v>
+      </c>
       <c r="L70" s="3"/>
-      <c r="M70" s="3"/>
+      <c r="M70" s="3" t="s">
+        <v>1452</v>
+      </c>
       <c r="N70" s="3"/>
-      <c r="O70" s="3"/>
+      <c r="O70" s="10" t="s">
+        <v>2004</v>
+      </c>
       <c r="P70" s="3"/>
       <c r="Q70" s="3"/>
       <c r="R70" s="3"/>
@@ -15859,7 +18337,7 @@
         <v>1147</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>1364</v>
@@ -15871,12 +18349,20 @@
       <c r="I71" s="3" t="s">
         <v>1584</v>
       </c>
-      <c r="J71" s="3"/>
-      <c r="K71" s="3"/>
+      <c r="J71" s="3" t="s">
+        <v>1683</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>1752</v>
+      </c>
       <c r="L71" s="3"/>
-      <c r="M71" s="3"/>
+      <c r="M71" s="3" t="s">
+        <v>1882</v>
+      </c>
       <c r="N71" s="3"/>
-      <c r="O71" s="3"/>
+      <c r="O71" s="3" t="s">
+        <v>2003</v>
+      </c>
       <c r="P71" s="3"/>
       <c r="Q71" s="3"/>
       <c r="R71" s="3"/>
@@ -15927,7 +18413,7 @@
         <v>1043</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>1365</v>
@@ -15939,12 +18425,20 @@
       <c r="I72" s="3" t="s">
         <v>1585</v>
       </c>
-      <c r="J72" s="3"/>
-      <c r="K72" s="3"/>
+      <c r="J72" s="3" t="s">
+        <v>1633</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>1753</v>
+      </c>
       <c r="L72" s="3"/>
-      <c r="M72" s="3"/>
+      <c r="M72" s="3" t="s">
+        <v>1671</v>
+      </c>
       <c r="N72" s="3"/>
-      <c r="O72" s="3"/>
+      <c r="O72" s="3" t="s">
+        <v>2005</v>
+      </c>
       <c r="P72" s="3"/>
       <c r="Q72" s="3"/>
       <c r="R72" s="3"/>
@@ -15995,7 +18489,7 @@
         <v>1148</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>1366</v>
@@ -16007,12 +18501,20 @@
       <c r="I73" s="3" t="s">
         <v>1586</v>
       </c>
-      <c r="J73" s="3"/>
-      <c r="K73" s="3"/>
+      <c r="J73" s="3" t="s">
+        <v>1685</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>1754</v>
+      </c>
       <c r="L73" s="3"/>
-      <c r="M73" s="3"/>
+      <c r="M73" s="3" t="s">
+        <v>1883</v>
+      </c>
       <c r="N73" s="3"/>
-      <c r="O73" s="3"/>
+      <c r="O73" s="3" t="s">
+        <v>2006</v>
+      </c>
       <c r="P73" s="3"/>
       <c r="Q73" s="3"/>
       <c r="R73" s="3"/>
@@ -16063,7 +18565,7 @@
         <v>1149</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>1313</v>
@@ -16075,12 +18577,20 @@
       <c r="I74" s="3" t="s">
         <v>1587</v>
       </c>
-      <c r="J74" s="3"/>
-      <c r="K74" s="3"/>
+      <c r="J74" s="3" t="s">
+        <v>1686</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>1755</v>
+      </c>
       <c r="L74" s="3"/>
-      <c r="M74" s="3"/>
+      <c r="M74" s="3" t="s">
+        <v>1884</v>
+      </c>
       <c r="N74" s="3"/>
-      <c r="O74" s="3"/>
+      <c r="O74" s="3" t="s">
+        <v>2007</v>
+      </c>
       <c r="P74" s="3"/>
       <c r="Q74" s="3"/>
       <c r="R74" s="3"/>
@@ -16131,7 +18641,7 @@
         <v>1057</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>1367</v>
@@ -16143,10 +18653,16 @@
       <c r="I75" s="3" t="s">
         <v>1588</v>
       </c>
-      <c r="J75" s="3"/>
-      <c r="K75" s="3"/>
+      <c r="J75" s="3" t="s">
+        <v>1687</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>1756</v>
+      </c>
       <c r="L75" s="3"/>
-      <c r="M75" s="3"/>
+      <c r="M75" s="3" t="s">
+        <v>1885</v>
+      </c>
       <c r="N75" s="3"/>
       <c r="O75" s="3"/>
       <c r="P75" s="3"/>
@@ -16199,7 +18715,7 @@
         <v>1150</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>1240</v>
+        <v>1263</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>1368</v>
@@ -16211,10 +18727,16 @@
       <c r="I76" s="3" t="s">
         <v>1589</v>
       </c>
-      <c r="J76" s="3"/>
-      <c r="K76" s="3"/>
+      <c r="J76" s="3" t="s">
+        <v>1688</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>1757</v>
+      </c>
       <c r="L76" s="3"/>
-      <c r="M76" s="3"/>
+      <c r="M76" s="3" t="s">
+        <v>1886</v>
+      </c>
       <c r="N76" s="3"/>
       <c r="O76" s="3"/>
       <c r="P76" s="3"/>
@@ -16267,7 +18789,7 @@
         <v>1151</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>1369</v>
@@ -16279,11 +18801,16 @@
       <c r="I77" s="3" t="s">
         <v>1258</v>
       </c>
-      <c r="J77" s="3"/>
-      <c r="K77" s="3"/>
+      <c r="J77" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>1758</v>
+      </c>
       <c r="L77" s="3"/>
-      <c r="M77" s="3"/>
-      <c r="N77" s="3"/>
+      <c r="M77" s="3" t="s">
+        <v>1887</v>
+      </c>
       <c r="O77" s="3"/>
       <c r="P77" s="3"/>
       <c r="Q77" s="3"/>
@@ -16335,7 +18862,7 @@
         <v>1152</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>1264</v>
+        <v>1241</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>1370</v>
@@ -16347,11 +18874,16 @@
       <c r="I78" s="3" t="s">
         <v>1590</v>
       </c>
-      <c r="J78" s="3"/>
-      <c r="K78" s="3"/>
+      <c r="J78" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>1759</v>
+      </c>
       <c r="L78" s="3"/>
-      <c r="M78" s="3"/>
-      <c r="N78" s="3"/>
+      <c r="M78" s="3" t="s">
+        <v>1888</v>
+      </c>
       <c r="O78" s="3"/>
       <c r="P78" s="3"/>
       <c r="Q78" s="3"/>
@@ -16403,7 +18935,7 @@
         <v>1153</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>1371</v>
@@ -16415,11 +18947,16 @@
       <c r="I79" s="3" t="s">
         <v>1591</v>
       </c>
-      <c r="J79" s="3"/>
-      <c r="K79" s="3"/>
+      <c r="J79" s="3" t="s">
+        <v>1690</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>1760</v>
+      </c>
       <c r="L79" s="3"/>
-      <c r="M79" s="3"/>
-      <c r="N79" s="3"/>
+      <c r="M79" s="3" t="s">
+        <v>1889</v>
+      </c>
       <c r="O79" s="3"/>
       <c r="P79" s="3"/>
       <c r="Q79" s="3"/>
@@ -16471,7 +19008,7 @@
         <v>1154</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>1251</v>
+        <v>1265</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>1304</v>
@@ -16483,11 +19020,16 @@
       <c r="I80" s="3" t="s">
         <v>1592</v>
       </c>
-      <c r="J80" s="3"/>
-      <c r="K80" s="3"/>
+      <c r="J80" s="3" t="s">
+        <v>1691</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>1761</v>
+      </c>
       <c r="L80" s="3"/>
-      <c r="M80" s="3"/>
-      <c r="N80" s="3"/>
+      <c r="M80" s="3" t="s">
+        <v>1890</v>
+      </c>
       <c r="O80" s="3"/>
       <c r="P80" s="3"/>
       <c r="Q80" s="3"/>
@@ -16539,7 +19081,7 @@
         <v>257</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>1238</v>
+        <v>1251</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>1372</v>
@@ -16551,11 +19093,16 @@
       <c r="I81" s="3" t="s">
         <v>1593</v>
       </c>
-      <c r="J81" s="3"/>
-      <c r="K81" s="3"/>
+      <c r="J81" s="3" t="s">
+        <v>1692</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>1762</v>
+      </c>
       <c r="L81" s="3"/>
-      <c r="M81" s="3"/>
-      <c r="N81" s="3"/>
+      <c r="M81" s="3" t="s">
+        <v>1891</v>
+      </c>
       <c r="O81" s="3"/>
       <c r="P81" s="3"/>
       <c r="Q81" s="3"/>
@@ -16607,7 +19154,7 @@
         <v>1157</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>1268</v>
+        <v>1238</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>1373</v>
@@ -16619,11 +19166,16 @@
       <c r="I82" s="3" t="s">
         <v>1594</v>
       </c>
-      <c r="J82" s="3"/>
-      <c r="K82" s="3"/>
+      <c r="J82" s="3" t="s">
+        <v>1693</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>1763</v>
+      </c>
       <c r="L82" s="3"/>
-      <c r="M82" s="3"/>
-      <c r="N82" s="3"/>
+      <c r="M82" s="3" t="s">
+        <v>1892</v>
+      </c>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
@@ -16675,7 +19227,7 @@
         <v>1155</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>1374</v>
@@ -16687,11 +19239,16 @@
       <c r="I83" s="3" t="s">
         <v>1555</v>
       </c>
-      <c r="J83" s="3"/>
-      <c r="K83" s="3"/>
+      <c r="J83" s="3" t="s">
+        <v>1677</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>1764</v>
+      </c>
       <c r="L83" s="3"/>
-      <c r="M83" s="3"/>
-      <c r="N83" s="3"/>
+      <c r="M83" s="3" t="s">
+        <v>1801</v>
+      </c>
       <c r="O83" s="3"/>
       <c r="P83" s="3"/>
       <c r="Q83" s="3"/>
@@ -16743,7 +19300,7 @@
         <v>1156</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>1375</v>
@@ -16756,10 +19313,13 @@
         <v>1595</v>
       </c>
       <c r="J84" s="3"/>
-      <c r="K84" s="3"/>
+      <c r="K84" s="3" t="s">
+        <v>1628</v>
+      </c>
       <c r="L84" s="3"/>
-      <c r="M84" s="3"/>
-      <c r="N84" s="3"/>
+      <c r="M84" s="3" t="s">
+        <v>1803</v>
+      </c>
       <c r="O84" s="3"/>
       <c r="P84" s="3"/>
       <c r="Q84" s="3"/>
@@ -16811,7 +19371,7 @@
         <v>1158</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>1376</v>
@@ -16824,10 +19384,13 @@
         <v>1596</v>
       </c>
       <c r="J85" s="3"/>
-      <c r="K85" s="3"/>
+      <c r="K85" s="3" t="s">
+        <v>1629</v>
+      </c>
       <c r="L85" s="3"/>
-      <c r="M85" s="3"/>
-      <c r="N85" s="3"/>
+      <c r="M85" s="3" t="s">
+        <v>1893</v>
+      </c>
       <c r="O85" s="3"/>
       <c r="P85" s="3"/>
       <c r="Q85" s="3"/>
@@ -16879,7 +19442,7 @@
         <v>259</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>1351</v>
@@ -16892,10 +19455,13 @@
         <v>1597</v>
       </c>
       <c r="J86" s="3"/>
-      <c r="K86" s="3"/>
+      <c r="K86" s="3" t="s">
+        <v>1765</v>
+      </c>
       <c r="L86" s="3"/>
-      <c r="M86" s="3"/>
-      <c r="N86" s="3"/>
+      <c r="M86" s="3" t="s">
+        <v>1894</v>
+      </c>
       <c r="O86" s="3"/>
       <c r="P86" s="3"/>
       <c r="Q86" s="3"/>
@@ -16947,7 +19513,7 @@
         <v>1159</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>1377</v>
@@ -16960,10 +19526,13 @@
         <v>1598</v>
       </c>
       <c r="J87" s="3"/>
-      <c r="K87" s="3"/>
+      <c r="K87" s="3" t="s">
+        <v>1766</v>
+      </c>
       <c r="L87" s="3"/>
-      <c r="M87" s="3"/>
-      <c r="N87" s="3"/>
+      <c r="M87" s="3" t="s">
+        <v>1886</v>
+      </c>
       <c r="O87" s="3"/>
       <c r="P87" s="3"/>
       <c r="Q87" s="3"/>
@@ -17015,7 +19584,7 @@
         <v>1160</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>1378</v>
@@ -17028,10 +19597,13 @@
         <v>1599</v>
       </c>
       <c r="J88" s="3"/>
-      <c r="K88" s="3"/>
+      <c r="K88" s="3" t="s">
+        <v>1767</v>
+      </c>
       <c r="L88" s="3"/>
-      <c r="M88" s="3"/>
-      <c r="N88" s="3"/>
+      <c r="M88" s="3" t="s">
+        <v>1643</v>
+      </c>
       <c r="O88" s="3"/>
       <c r="P88" s="3"/>
       <c r="Q88" s="3"/>
@@ -17081,7 +19653,7 @@
         <v>1161</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>1379</v>
@@ -17094,10 +19666,13 @@
         <v>1600</v>
       </c>
       <c r="J89" s="3"/>
-      <c r="K89" s="3"/>
+      <c r="K89" s="3" t="s">
+        <v>1768</v>
+      </c>
       <c r="L89" s="3"/>
-      <c r="M89" s="3"/>
-      <c r="N89" s="3"/>
+      <c r="M89" s="3" t="s">
+        <v>1895</v>
+      </c>
       <c r="O89" s="3"/>
       <c r="P89" s="3"/>
       <c r="Q89" s="3"/>
@@ -17147,7 +19722,7 @@
         <v>1162</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>1380</v>
@@ -17157,13 +19732,16 @@
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="3" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="J90" s="3"/>
-      <c r="K90" s="3"/>
+      <c r="K90" s="3" t="s">
+        <v>1769</v>
+      </c>
       <c r="L90" s="3"/>
-      <c r="M90" s="3"/>
-      <c r="N90" s="3"/>
+      <c r="M90" s="3" t="s">
+        <v>1896</v>
+      </c>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
@@ -17213,7 +19791,7 @@
         <v>1163</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>1381</v>
@@ -17223,13 +19801,16 @@
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="3" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="J91" s="3"/>
-      <c r="K91" s="3"/>
+      <c r="K91" s="3" t="s">
+        <v>1770</v>
+      </c>
       <c r="L91" s="3"/>
-      <c r="M91" s="3"/>
-      <c r="N91" s="3"/>
+      <c r="M91" s="3" t="s">
+        <v>1379</v>
+      </c>
       <c r="O91" s="3"/>
       <c r="P91" s="3"/>
       <c r="Q91" s="3"/>
@@ -17279,7 +19860,7 @@
         <v>261</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>1382</v>
@@ -17292,9 +19873,13 @@
         <v>1574</v>
       </c>
       <c r="J92" s="3"/>
-      <c r="K92" s="3"/>
+      <c r="K92" s="3" t="s">
+        <v>1771</v>
+      </c>
       <c r="L92" s="3"/>
-      <c r="M92" s="3"/>
+      <c r="M92" s="3" t="s">
+        <v>1377</v>
+      </c>
       <c r="N92" s="3"/>
       <c r="O92" s="3"/>
       <c r="P92" s="3"/>
@@ -17345,7 +19930,7 @@
         <v>1164</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>1383</v>
@@ -17356,9 +19941,13 @@
         <v>1575</v>
       </c>
       <c r="J93" s="3"/>
-      <c r="K93" s="3"/>
+      <c r="K93" s="3" t="s">
+        <v>1772</v>
+      </c>
       <c r="L93" s="3"/>
-      <c r="M93" s="3"/>
+      <c r="M93" s="3" t="s">
+        <v>1897</v>
+      </c>
       <c r="N93" s="3"/>
       <c r="O93" s="3"/>
       <c r="P93" s="3"/>
@@ -17409,7 +19998,7 @@
         <v>255</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>1384</v>
@@ -17417,12 +20006,16 @@
       <c r="G94" s="3"/>
       <c r="H94" s="3"/>
       <c r="I94" s="3" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="J94" s="3"/>
-      <c r="K94" s="3"/>
+      <c r="K94" s="3" t="s">
+        <v>1773</v>
+      </c>
       <c r="L94" s="3"/>
-      <c r="M94" s="3"/>
+      <c r="M94" s="3" t="s">
+        <v>1898</v>
+      </c>
       <c r="N94" s="3"/>
       <c r="O94" s="3"/>
       <c r="P94" s="3"/>
@@ -17473,7 +20066,7 @@
         <v>1165</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>1385</v>
@@ -17481,12 +20074,16 @@
       <c r="G95" s="3"/>
       <c r="H95" s="3"/>
       <c r="I95" s="3" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="J95" s="3"/>
-      <c r="K95" s="3"/>
+      <c r="K95" s="3" t="s">
+        <v>1774</v>
+      </c>
       <c r="L95" s="3"/>
-      <c r="M95" s="3"/>
+      <c r="M95" s="3" t="s">
+        <v>1899</v>
+      </c>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
@@ -17537,7 +20134,7 @@
         <v>1166</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>1386</v>
@@ -17545,12 +20142,16 @@
       <c r="G96" s="3"/>
       <c r="H96" s="3"/>
       <c r="I96" s="3" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="J96" s="3"/>
-      <c r="K96" s="3"/>
+      <c r="K96" s="3" t="s">
+        <v>1775</v>
+      </c>
       <c r="L96" s="3"/>
-      <c r="M96" s="3"/>
+      <c r="M96" s="3" t="s">
+        <v>1810</v>
+      </c>
       <c r="N96" s="3"/>
       <c r="O96" s="3"/>
       <c r="P96" s="3"/>
@@ -17601,7 +20202,7 @@
         <v>1167</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>1394</v>
@@ -17609,12 +20210,16 @@
       <c r="G97" s="3"/>
       <c r="H97" s="3"/>
       <c r="I97" s="3" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="J97" s="3"/>
-      <c r="K97" s="3"/>
+      <c r="K97" s="3" t="s">
+        <v>1776</v>
+      </c>
       <c r="L97" s="3"/>
-      <c r="M97" s="3"/>
+      <c r="M97" s="3" t="s">
+        <v>1812</v>
+      </c>
       <c r="N97" s="3"/>
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
@@ -17665,7 +20270,7 @@
         <v>1168</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>1387</v>
@@ -17673,12 +20278,16 @@
       <c r="G98" s="3"/>
       <c r="H98" s="3"/>
       <c r="I98" s="3" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="J98" s="3"/>
-      <c r="K98" s="3"/>
+      <c r="K98" s="3" t="s">
+        <v>1777</v>
+      </c>
       <c r="L98" s="3"/>
-      <c r="M98" s="3"/>
+      <c r="M98" s="3" t="s">
+        <v>1900</v>
+      </c>
       <c r="N98" s="3"/>
       <c r="O98" s="3"/>
       <c r="P98" s="3"/>
@@ -17729,7 +20338,7 @@
         <v>1169</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>1258</v>
+        <v>1283</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>1390</v>
@@ -17737,10 +20346,12 @@
       <c r="G99" s="3"/>
       <c r="H99" s="3"/>
       <c r="I99" s="3" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="J99" s="3"/>
-      <c r="K99" s="3"/>
+      <c r="K99" s="3" t="s">
+        <v>1719</v>
+      </c>
       <c r="L99" s="3"/>
       <c r="M99" s="3"/>
       <c r="N99" s="3"/>
@@ -17793,7 +20404,7 @@
         <v>263</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>1284</v>
+        <v>1258</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>1389</v>
@@ -17801,10 +20412,12 @@
       <c r="G100" s="3"/>
       <c r="H100" s="3"/>
       <c r="I100" s="3" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="J100" s="3"/>
-      <c r="K100" s="3"/>
+      <c r="K100" s="3" t="s">
+        <v>1778</v>
+      </c>
       <c r="L100" s="3"/>
       <c r="M100" s="3"/>
       <c r="N100" s="3"/>
@@ -17857,7 +20470,7 @@
         <v>264</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>1391</v>
@@ -17865,10 +20478,12 @@
       <c r="G101" s="3"/>
       <c r="H101" s="3"/>
       <c r="I101" s="3" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="J101" s="3"/>
-      <c r="K101" s="3"/>
+      <c r="K101" s="3" t="s">
+        <v>1779</v>
+      </c>
       <c r="L101" s="3"/>
       <c r="M101" s="3"/>
       <c r="N101" s="3"/>
@@ -17921,7 +20536,7 @@
         <v>262</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>1392</v>
@@ -17929,10 +20544,12 @@
       <c r="G102" s="3"/>
       <c r="H102" s="3"/>
       <c r="I102" s="3" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="J102" s="3"/>
-      <c r="K102" s="3"/>
+      <c r="K102" s="3" t="s">
+        <v>1780</v>
+      </c>
       <c r="L102" s="3"/>
       <c r="M102" s="3"/>
       <c r="N102" s="3"/>
@@ -17985,7 +20602,7 @@
         <v>1170</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>1393</v>
@@ -17993,10 +20610,12 @@
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
       <c r="I103" s="3" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="J103" s="3"/>
-      <c r="K103" s="3"/>
+      <c r="K103" s="3" t="s">
+        <v>1781</v>
+      </c>
       <c r="L103" s="3"/>
       <c r="M103" s="3"/>
       <c r="N103" s="3"/>
@@ -18049,7 +20668,7 @@
         <v>1171</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>1350</v>
@@ -18057,10 +20676,12 @@
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
       <c r="I104" s="3" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="J104" s="3"/>
-      <c r="K104" s="3"/>
+      <c r="K104" s="3" t="s">
+        <v>1782</v>
+      </c>
       <c r="L104" s="3"/>
       <c r="M104" s="3"/>
       <c r="N104" s="3"/>
@@ -18113,7 +20734,7 @@
         <v>261</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>1388</v>
@@ -18121,10 +20742,12 @@
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
       <c r="I105" s="3" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="J105" s="3"/>
-      <c r="K105" s="3"/>
+      <c r="K105" s="3" t="s">
+        <v>1783</v>
+      </c>
       <c r="L105" s="3"/>
       <c r="M105" s="3"/>
       <c r="N105" s="3"/>
@@ -18177,16 +20800,18 @@
         <v>255</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
       <c r="I106" s="3" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="J106" s="3"/>
-      <c r="K106" s="3"/>
+      <c r="K106" s="3" t="s">
+        <v>1740</v>
+      </c>
       <c r="L106" s="3"/>
       <c r="M106" s="3"/>
       <c r="N106" s="3"/>
@@ -18239,16 +20864,18 @@
         <v>927</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
       <c r="I107" s="3" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="J107" s="3"/>
-      <c r="K107" s="3"/>
+      <c r="K107" s="3" t="s">
+        <v>1741</v>
+      </c>
       <c r="L107" s="3"/>
       <c r="M107" s="3"/>
       <c r="N107" s="3"/>
@@ -18301,16 +20928,18 @@
         <v>926</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
       <c r="I108" s="3" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="J108" s="3"/>
-      <c r="K108" s="3"/>
+      <c r="K108" s="3" t="s">
+        <v>1751</v>
+      </c>
       <c r="L108" s="3"/>
       <c r="M108" s="3"/>
       <c r="N108" s="3"/>
@@ -18361,16 +20990,18 @@
         <v>1172</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3"/>
       <c r="H109" s="3"/>
       <c r="I109" s="3" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="J109" s="3"/>
-      <c r="K109" s="3"/>
+      <c r="K109" s="3" t="s">
+        <v>1784</v>
+      </c>
       <c r="L109" s="3"/>
       <c r="M109" s="3"/>
       <c r="N109" s="3"/>
@@ -18421,16 +21052,18 @@
         <v>1173</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="F110" s="3"/>
       <c r="G110" s="3"/>
       <c r="H110" s="3"/>
       <c r="I110" s="3" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="J110" s="3"/>
-      <c r="K110" s="3"/>
+      <c r="K110" s="3" t="s">
+        <v>1785</v>
+      </c>
       <c r="L110" s="3"/>
       <c r="M110" s="3"/>
       <c r="N110" s="3"/>
@@ -18481,16 +21114,18 @@
         <v>1174</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="F111" s="3"/>
       <c r="G111" s="3"/>
       <c r="H111" s="3"/>
       <c r="I111" s="3" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="J111" s="3"/>
-      <c r="K111" s="3"/>
+      <c r="K111" s="3" t="s">
+        <v>1786</v>
+      </c>
       <c r="L111" s="3"/>
       <c r="M111" s="3"/>
       <c r="N111" s="3"/>
@@ -18541,7 +21176,7 @@
         <v>1175</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="F112" s="3"/>
       <c r="G112" s="3"/>
@@ -18601,7 +21236,7 @@
         <v>1176</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="F113" s="3"/>
       <c r="G113" s="3"/>
@@ -18661,7 +21296,7 @@
         <v>1158</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="F114" s="3"/>
       <c r="G114" s="3"/>
@@ -18718,7 +21353,9 @@
       <c r="D115" s="3" t="s">
         <v>1177</v>
       </c>
-      <c r="E115" s="3"/>
+      <c r="E115" s="3" t="s">
+        <v>1298</v>
+      </c>
       <c r="F115" s="3"/>
       <c r="G115" s="3"/>
       <c r="H115" s="3"/>
@@ -19609,6 +22246,21 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" display="https://www.bilibili.com/video/BV1Zt4y1G7AY/?p=11" xr:uid="{9A1807D6-EF19-4A6B-8491-33809D8AC08F}"/>
+    <hyperlink ref="K1" r:id="rId2" display="https://www.bilibili.com/video/BV1Zt4y1G7AY/?p=12" xr:uid="{90DCDCC0-A416-4154-81ED-A5AF615AE570}"/>
+    <hyperlink ref="A1" r:id="rId3" display="https://www.bilibili.com/video/BV1Zt4y1G7AY/?p=1" xr:uid="{0D76E68B-608E-4289-ADA9-541FB12C4D47}"/>
+    <hyperlink ref="B1" r:id="rId4" display="https://www.bilibili.com/video/BV1Zt4y1G7AY/?p=3" xr:uid="{BA5B8B2E-EE5B-4D80-A507-FB42EE5949A9}"/>
+    <hyperlink ref="C1" r:id="rId5" display="https://www.bilibili.com/video/BV1Zt4y1G7AY/?p=4" xr:uid="{377F2DB7-2877-4C07-9F86-2943A0DD0A86}"/>
+    <hyperlink ref="D1" r:id="rId6" display="https://www.bilibili.com/video/BV1Zt4y1G7AY/?p=5" xr:uid="{F5AE4968-1C07-4AE5-B5EE-B331C53D2C03}"/>
+    <hyperlink ref="E1" r:id="rId7" display="https://www.bilibili.com/video/BV1Zt4y1G7AY/?p=6" xr:uid="{B4D80994-8A11-4B31-B111-0B56F27C5E76}"/>
+    <hyperlink ref="F1" r:id="rId8" display="https://www.bilibili.com/video/BV1Zt4y1G7AY/?p=7" xr:uid="{7A603FAC-6C51-46A6-935E-B52664BC2D61}"/>
+    <hyperlink ref="G1" r:id="rId9" display="https://www.bilibili.com/video/BV1Zt4y1G7AY/?p=8" xr:uid="{23289583-0AF0-4A41-A3AB-3A369AB53361}"/>
+    <hyperlink ref="H1" r:id="rId10" display="https://www.bilibili.com/video/BV1Zt4y1G7AY/?p=9" xr:uid="{42A59954-3A70-4DB4-A12B-3E2312DD68F3}"/>
+    <hyperlink ref="I1" r:id="rId11" display="https://www.bilibili.com/video/BV1Zt4y1G7AY/?p=10" xr:uid="{1BA3EBA1-67BF-40F1-91F9-735DCA222EA3}"/>
+    <hyperlink ref="L1" r:id="rId12" display="https://www.bilibili.com/video/BV1Zt4y1G7AY/?p=13" xr:uid="{3857AB41-46C6-4863-ABB9-C934250CEE52}"/>
+    <hyperlink ref="M1" r:id="rId13" display="https://www.bilibili.com/video/BV1Zt4y1G7AY/?p=14" xr:uid="{6393F239-3044-45DC-A918-1926417F7CB3}"/>
+    <hyperlink ref="N1" r:id="rId14" display="https://www.bilibili.com/video/BV1Zt4y1G7AY/?p=15" xr:uid="{B129FF67-571E-4072-A8ED-35B7BDB28E7A}"/>
+    <hyperlink ref="O1" r:id="rId15" display="https://www.bilibili.com/video/BV1Zt4y1G7AY/?p=16" xr:uid="{7260A34D-DAE3-4E7B-883E-BEFC42FC7170}"/>
+    <hyperlink ref="P1" r:id="rId16" display="https://www.bilibili.com/video/BV1Zt4y1G7AY/?p=17" xr:uid="{8D1DADFB-37B4-42AF-B406-47FBD41E9005}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
